--- a/Data/testDataCzechia_PK14.xlsx
+++ b/Data/testDataCzechia_PK14.xlsx
@@ -1,35 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{21CF1068-E503-4FE4-A307-6B3D59C9867C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet sheetId="2" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1001" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="221">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -256,10 +241,16 @@
     <t>ProposedPayGroupFinal</t>
   </si>
   <si>
-    <t>10697324</t>
-  </si>
-  <si>
-    <t>Passed</t>
+    <t>Test1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test failed for 'Olaf Bartell' Employee:{undefined}TimeoutError: page.goto: Timeout 30000ms exceeded.
+Call log:
+  [2m- navigating to "https://wd3-impl.workday.com/wday/authgwy/primark14/login.htmld", waiting until "load"[22m
+</t>
+  </si>
+  <si>
+    <t>Failed</t>
   </si>
   <si>
     <t>895 Retail Team 1 (Jaziz Wezupa (10573442) (Inherited))</t>
@@ -268,10 +259,10 @@
     <t>Czechia</t>
   </si>
   <si>
-    <t>CzechiaOne</t>
-  </si>
-  <si>
-    <t>PayrollTwentyFiveFebTwentySix</t>
+    <t>Olaf</t>
+  </si>
+  <si>
+    <t>Bartell</t>
   </si>
   <si>
     <t>770 272 784</t>
@@ -409,19 +400,16 @@
     <t>CZ Monthly</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'CzechiaTwo PayrollTwentyFiveFebTwentySix' Employee:{}TimeoutError: locator.click: Timeout 30000ms exceeded.
-Call log:
-  [2m- waiting for locator('//label[contains(.,\'Hire Date\')]/parent::div/following-sibling::div/descendant::input[@data-automation-id=\'dateSectionDay-input\']')[22m
-</t>
-  </si>
-  <si>
-    <t>Failed</t>
+    <t>Test2</t>
   </si>
   <si>
     <t>895 Store Management (Jaziz Wezupa (10573442))</t>
   </si>
   <si>
-    <t>CzechiaTwo</t>
+    <t>Verona</t>
+  </si>
+  <si>
+    <t>Wiza</t>
   </si>
   <si>
     <t>Auto 48962562</t>
@@ -442,13 +430,7 @@
     <t>Aina</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'CzechiaThree PayrollTwentyFiveFebTwentySix' Employee:{}TimeoutError: locator.click: Timeout 30000ms exceeded.
-Call log:
-  [2m- waiting for locator('//label[contains(.,\'Hire Date\')]/parent::div/following-sibling::div/descendant::input[@data-automation-id=\'dateSectionDay-input\']')[22m
-</t>
-  </si>
-  <si>
-    <t>CzechiaThree</t>
+    <t>Test3</t>
   </si>
   <si>
     <t>Fixed Term (Fixed Term)</t>
@@ -478,247 +460,7 @@
     <t>Ogbonda</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'CzechiaFour PayrollTwentyFiveFebTwentySix' Employee:{}TimeoutError: locator.clear: Timeout 30000ms exceeded.
-Call log:
-  [2m- waiting for locator('//label[contains(.,\'End Employment Date\')]/parent::div/following-sibling::div/descendant::input[@data-automation-id=\'dateSectionDay-input\']')[22m
-[2m  -   locator resolved to &lt;input min="1" max="31" value="" width="2ch" tabindex="…/&gt;[22m
-[2m  -   fill("")[22m
-[2m  - attempting fill action[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #1[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #2[22m
-[2m  -   waiting 20ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #3[22m
-[2m  -   waiting 100ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #4[22m
-[2m  -   waiting 100ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #5[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #6[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #7[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #8[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #9[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #10[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #11[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #12[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #13[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #14[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #15[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #16[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #17[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #18[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #19[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #20[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #21[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #22[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #23[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #24[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #25[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #26[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #27[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #28[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #29[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #30[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #31[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #32[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #33[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #34[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #35[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #36[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #37[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #38[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #39[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #40[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #41[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #42[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #43[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #44[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #45[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #46[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #47[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #48[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #49[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #50[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #51[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #52[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #53[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #54[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #55[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #56[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #57[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #58[22m
-[2m  -   waiting 500ms[22m
-</t>
-  </si>
-  <si>
-    <t>CzechiaFour</t>
+    <t>Test4</t>
   </si>
   <si>
     <t>Auto 73452255</t>
@@ -742,13 +484,7 @@
     <t>Obot</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'CzechiaFive PayrollTwentyFiveFebTwentySix' Employee:{}TimeoutError: locator.focus: Timeout 30000ms exceeded.
-Call log:
-  [2m- waiting for getByLabel('Position').first()[22m
-</t>
-  </si>
-  <si>
-    <t>CzechiaFive</t>
+    <t>Test5</t>
   </si>
   <si>
     <t>Students</t>
@@ -775,10 +511,7 @@
     <t>Yusuf</t>
   </si>
   <si>
-    <t>Test failed for 'CzechiaSix PayrollTwentyFiveFebTwentySix' Employee: Errors and AlertsAlertsNational IDs (Row 1)This national identifier you entered is already in use. Verify that the information is accurate.National IDs (Row 2)This national identifier you entered is already in use. Verify that the information is accurate. &amp; find failed Screenshot Path:-&gt;H:\Latest_Workday_Playwright/WorkdayFailedScreenshot/2025-02-26T05-29-19-003Z.png</t>
-  </si>
-  <si>
-    <t>CzechiaSix</t>
+    <t>Test6</t>
   </si>
   <si>
     <t>771 272 784</t>
@@ -805,13 +538,7 @@
     <t>Torunarigha</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'CzechiaSeven PayrollTwentyFiveFebTwentySix' Employee:{10697326}TimeoutError: locator.focus: Timeout 30000ms exceeded.
-Call log:
-  [2m- waiting for getByLabel('Position').first()[22m
-</t>
-  </si>
-  <si>
-    <t>CzechiaSeven</t>
+    <t>Test7</t>
   </si>
   <si>
     <t>772 272 784</t>
@@ -829,247 +556,7 @@
     <t>Ekong</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'CzechiaEight PayrollTwentyFiveFebTwentySix' Employee:{}TimeoutError: locator.clear: Timeout 30000ms exceeded.
-Call log:
-  [2m- waiting for locator('//label[contains(.,\'End Employment Date\')]/parent::div/following-sibling::div/descendant::input[@data-automation-id=\'dateSectionDay-input\']')[22m
-[2m  -   locator resolved to &lt;input min="1" max="31" value="" width="2ch" tabindex="…/&gt;[22m
-[2m  -   fill("")[22m
-[2m  - attempting fill action[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #1[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #2[22m
-[2m  -   waiting 20ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #3[22m
-[2m  -   waiting 100ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #4[22m
-[2m  -   waiting 100ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #5[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #6[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #7[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #8[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #9[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #10[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #11[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #12[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #13[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #14[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #15[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #16[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #17[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #18[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #19[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #20[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #21[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #22[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #23[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #24[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #25[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #26[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #27[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #28[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #29[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #30[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #31[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #32[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #33[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #34[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #35[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #36[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #37[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #38[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #39[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #40[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #41[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #42[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #43[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #44[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #45[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #46[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #47[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #48[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #49[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #50[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #51[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #52[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #53[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #54[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #55[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #56[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #57[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #58[22m
-[2m  -   waiting 500ms[22m
-</t>
-  </si>
-  <si>
-    <t>CzechiaEight</t>
+    <t>Test8</t>
   </si>
   <si>
     <t>773 272 784</t>
@@ -1087,13 +574,7 @@
     <t>Sanusi</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'CzechiaNine PayrollTwentyFiveFebTwentySix' Employee:{}TimeoutError: locator.focus: Timeout 30000ms exceeded.
-Call log:
-  [2m- waiting for getByLabel('Position').first()[22m
-</t>
-  </si>
-  <si>
-    <t>CzechiaNine</t>
+    <t>Test9</t>
   </si>
   <si>
     <t>774 272 784</t>
@@ -1108,10 +589,7 @@
     <t>Ajayi</t>
   </si>
   <si>
-    <t>Test failed for 'CzechiaTen PayrollTwentyFiveFebTwentySix' Employee: Errors and AlertsAlertsNational IDs (Row 1)This national identifier you entered is already in use. Verify that the information is accurate.National IDs (Row 2)This national identifier you entered is already in use. Verify that the information is accurate. &amp; find failed Screenshot Path:-&gt;H:\Latest_Workday_Playwright/WorkdayFailedScreenshot/2025-02-26T05-43-31-466Z.png</t>
-  </si>
-  <si>
-    <t>CzechiaTen</t>
+    <t>Test10</t>
   </si>
   <si>
     <t>775 272 784</t>
@@ -1129,13 +607,7 @@
     <t>Awaziem</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'CzechiaEleven PayrollTwentyFiveFebTwentySix' Employee:{10697327}TimeoutError: locator.focus: Timeout 30000ms exceeded.
-Call log:
-  [2m- waiting for getByLabel('Position').first()[22m
-</t>
-  </si>
-  <si>
-    <t>CzechiaEleven</t>
+    <t>Test11</t>
   </si>
   <si>
     <t>776 272 784</t>
@@ -1153,247 +625,7 @@
     <t>Ughelumba</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'CzechiaTwelve PayrollTwentyFiveFebTwentySix' Employee:{}TimeoutError: locator.clear: Timeout 30000ms exceeded.
-Call log:
-  [2m- waiting for locator('//label[contains(.,\'End Employment Date\')]/parent::div/following-sibling::div/descendant::input[@data-automation-id=\'dateSectionDay-input\']')[22m
-[2m  -   locator resolved to &lt;input min="1" max="31" value="" width="2ch" tabindex="…/&gt;[22m
-[2m  -   fill("")[22m
-[2m  - attempting fill action[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #1[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #2[22m
-[2m  -   waiting 20ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #3[22m
-[2m  -   waiting 100ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #4[22m
-[2m  -   waiting 100ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #5[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #6[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #7[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #8[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #9[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #10[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #11[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #12[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #13[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #14[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #15[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #16[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #17[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #18[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #19[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #20[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #21[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #22[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #23[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #24[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #25[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #26[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #27[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #28[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #29[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #30[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #31[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #32[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #33[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #34[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #35[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #36[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #37[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #38[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #39[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #40[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #41[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #42[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #43[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #44[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #45[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #46[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #47[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #48[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #49[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #50[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #51[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #52[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #53[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #54[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #55[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #56[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #57[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and editable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying fill action, attempt #58[22m
-[2m  -   waiting 500ms[22m
-</t>
-  </si>
-  <si>
-    <t>CzechiaTwelve</t>
+    <t>Test12</t>
   </si>
   <si>
     <t>777 272 784</t>
@@ -1411,13 +643,7 @@
     <t>Ebuehi</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'CzechiaThirteen PayrollTwentyFiveFebTwentySix' Employee:{}TimeoutError: locator.focus: Timeout 30000ms exceeded.
-Call log:
-  [2m- waiting for getByLabel('Position').first()[22m
-</t>
-  </si>
-  <si>
-    <t>CzechiaThirteen</t>
+    <t>Test13</t>
   </si>
   <si>
     <t>778 272 784</t>
@@ -1432,13 +658,7 @@
     <t>Omeruo</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'CzechiaFourteen PayrollTwentyFiveFebTwentySix' Employee:{}TimeoutError: locator.focus: Timeout 30000ms exceeded.
-Call log:
-  [2m- waiting for getByLabel('Position').first()[22m
-</t>
-  </si>
-  <si>
-    <t>CzechiaFourteen</t>
+    <t>Test14</t>
   </si>
   <si>
     <t>779 272 784</t>
@@ -1450,13 +670,7 @@
     <t>Dele Bashiru</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'CzechiaFifteen PayrollTwentyFiveFebTwentySix' Employee:{}TimeoutError: locator.focus: Timeout 30000ms exceeded.
-Call log:
-  [2m- waiting for getByLabel('Position').first()[22m
-</t>
-  </si>
-  <si>
-    <t>CzechiaFifteen</t>
+    <t>Test15</t>
   </si>
   <si>
     <t>255 Stockroom</t>
@@ -1471,49 +685,54 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="12"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <color theme="1"/>
+      <family val="1"/>
       <sz val="12"/>
-      <color theme="1"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
+      <color theme="1"/>
+      <family val="1"/>
       <sz val="14"/>
-      <color theme="1"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
+      <color theme="1"/>
+      <family val="1"/>
       <sz val="10"/>
-      <color theme="1"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
       <u/>
+      <color theme="1"/>
+      <family val="1"/>
       <sz val="10"/>
-      <color theme="1"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
+    </font>
+    <font>
+      <family val="2"/>
+      <sz val="14"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="7">
@@ -1525,7 +744,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.79998168889431442"/>
+        <fgColor theme="3" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1565,35 +784,23 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <right style="thin"/>
+      <top style="thin"/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1638,8 +845,14 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1919,10 +1132,10 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CN16"/>
-  <sheetFormatPr defaultRowHeight="15.6" customHeight="1" x14ac:dyDescent="0.3"/>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:CN17"/>
+  <sheetFormatPr defaultRowHeight="15.6" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.21875" style="1" customWidth="1"/>
     <col min="2" max="2" width="12" style="1" customWidth="1"/>
@@ -1969,12 +1182,12 @@
     <col min="43" max="43" width="20.109375" style="1" customWidth="1"/>
     <col min="44" max="44" width="10.6640625" style="1" customWidth="1"/>
     <col min="45" max="45" width="19" style="1" customWidth="1"/>
-    <col min="46" max="46" width="13.5546875" style="1" customWidth="1"/>
+    <col min="46" max="46" width="15.77734375" style="1" customWidth="1"/>
     <col min="47" max="47" width="13.6640625" style="1" customWidth="1"/>
     <col min="48" max="48" width="17.77734375" style="1" customWidth="1"/>
     <col min="49" max="49" width="10.6640625" style="1" customWidth="1"/>
     <col min="50" max="50" width="19" style="1" customWidth="1"/>
-    <col min="51" max="51" width="13.5546875" style="1" customWidth="1"/>
+    <col min="51" max="51" width="14.33203125" style="1" customWidth="1"/>
     <col min="52" max="52" width="13.6640625" style="1" customWidth="1"/>
     <col min="53" max="53" width="17.77734375" style="1" customWidth="1"/>
     <col min="54" max="54" width="8.5546875" style="1" customWidth="1"/>
@@ -2003,11 +1216,10 @@
     <col min="77" max="77" width="15" style="1" customWidth="1"/>
     <col min="78" max="78" width="33.6640625" style="1" customWidth="1"/>
     <col min="79" max="79" width="26.88671875" style="1" customWidth="1"/>
-    <col min="80" max="80" width="8.88671875" style="1" customWidth="1"/>
-    <col min="81" max="16384" width="8.88671875" style="1"/>
+    <col min="80" max="16384" width="8.88671875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:92" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="18" customHeight="1" spans="1:92" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2259,43 +1471,45 @@
       <c r="CM1" s="1"/>
       <c r="CN1" s="1"/>
     </row>
-    <row r="2" spans="1:92" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8"/>
+    <row r="2" ht="15" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>75</v>
+      </c>
       <c r="B2" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K2" s="12">
         <v>45597</v>
       </c>
       <c r="L2" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M2" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N2" s="10">
         <v>1</v>
@@ -2304,72 +1518,72 @@
         <v>213111231</v>
       </c>
       <c r="P2" s="11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q2" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="R2" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="R2" s="11" t="s">
-        <v>85</v>
-      </c>
       <c r="S2" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T2" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U2" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="V2" s="14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="W2" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X2" s="12">
         <f t="shared" ref="X2:X16" si="0">K2</f>
         <v>45597</v>
       </c>
       <c r="Y2" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Z2" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AA2" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AB2" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AC2" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AD2" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AE2" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF2" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG2" s="15">
         <v>40</v>
       </c>
       <c r="AH2" s="12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AI2" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AJ2" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="AK2" s="12" t="str">
+        <v>101</v>
+      </c>
+      <c r="AK2" s="12">
         <f t="shared" ref="AK2:AK16" si="1">AH2</f>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AL2" s="12">
         <f t="shared" ref="AL2:AL16" si="2">K2</f>
@@ -2380,10 +1594,10 @@
         <v>45597</v>
       </c>
       <c r="AN2" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO2" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AP2" s="10">
         <v>100</v>
@@ -2393,79 +1607,79 @@
         <v>45687</v>
       </c>
       <c r="AR2" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AS2" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="AT2" s="10">
-        <v>9661114199</v>
+        <v>104</v>
+      </c>
+      <c r="AT2" s="17">
+        <v>9661119061</v>
       </c>
       <c r="AU2" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AV2" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="AW2" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AX2" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="AY2" s="17">
+        <v>144042793</v>
+      </c>
+      <c r="AZ2" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="AW2" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="AX2" s="16" t="s">
+      <c r="BA2" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="AY2" s="10">
-        <v>144842713</v>
-      </c>
-      <c r="AZ2" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="BA2" s="12" t="s">
-        <v>105</v>
-      </c>
       <c r="BB2" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="BC2" s="12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BD2" s="16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="BE2" s="16" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BF2" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BG2" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BH2" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BI2" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BJ2" s="16" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BK2" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="BL2" s="13" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="BM2" s="13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="BN2" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BO2" s="13">
         <v>2000</v>
       </c>
       <c r="BP2" s="13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BQ2" s="13">
         <v>1995</v>
@@ -2474,70 +1688,68 @@
         <v>2000</v>
       </c>
       <c r="BS2" s="13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BT2" s="13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BU2" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="BV2" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="BW2" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="BV2" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="BX2" s="17">
+      <c r="BW2" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="BX2" s="18">
         <v>111</v>
       </c>
-      <c r="BY2" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="BZ2" s="17" t="s">
+      <c r="BY2" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="CA2" s="17" t="s">
+      <c r="BZ2" s="18" t="s">
         <v>125</v>
       </c>
+      <c r="CA2" s="18" t="s">
+        <v>126</v>
+      </c>
     </row>
-    <row r="3" spans="1:92" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="C3" s="8" t="s">
+    <row r="3" ht="15" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
         <v>127</v>
       </c>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
       <c r="D3" s="9" t="s">
         <v>128</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>129</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K3" s="12">
         <v>45597</v>
       </c>
       <c r="L3" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M3" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N3" s="10">
         <v>1</v>
@@ -2546,72 +1758,72 @@
         <v>213111231</v>
       </c>
       <c r="P3" s="11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q3" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="R3" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="R3" s="11" t="s">
-        <v>85</v>
-      </c>
       <c r="S3" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T3" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U3" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="V3" s="14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="W3" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X3" s="12">
         <f t="shared" si="0"/>
         <v>45597</v>
       </c>
       <c r="Y3" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Z3" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AA3" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AB3" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AC3" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AD3" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AE3" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF3" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG3" s="15">
         <v>40</v>
       </c>
       <c r="AH3" s="12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AI3" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AJ3" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="AK3" s="12" t="str">
+        <v>101</v>
+      </c>
+      <c r="AK3" s="12">
         <f t="shared" si="1"/>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AL3" s="12">
         <f t="shared" si="2"/>
@@ -2622,10 +1834,10 @@
         <v>45597</v>
       </c>
       <c r="AN3" s="11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AO3" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AP3" s="10">
         <v>100</v>
@@ -2635,79 +1847,79 @@
         <v>45687</v>
       </c>
       <c r="AR3" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AS3" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="AT3" s="10">
-        <v>9661116652</v>
+        <v>104</v>
+      </c>
+      <c r="AT3" s="17">
+        <v>9661117455</v>
       </c>
       <c r="AU3" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AV3" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="AW3" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AX3" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="AY3" s="17">
+        <v>144032794</v>
+      </c>
+      <c r="AZ3" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="AW3" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="AX3" s="16" t="s">
+      <c r="BA3" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="AY3" s="10">
-        <v>144832714</v>
-      </c>
-      <c r="AZ3" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="BA3" s="12" t="s">
-        <v>105</v>
-      </c>
       <c r="BB3" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="BC3" s="12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BD3" s="16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="BE3" s="16" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BF3" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BG3" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BH3" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BI3" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BJ3" s="16" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BK3" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="BL3" s="13" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="BM3" s="13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="BN3" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BO3" s="13">
         <v>2000</v>
       </c>
       <c r="BP3" s="13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BQ3" s="13">
         <v>1995</v>
@@ -2716,70 +1928,64 @@
         <v>2000</v>
       </c>
       <c r="BS3" s="13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BT3" s="13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BU3" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="BV3" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="BW3" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="BX3" s="18">
+        <v>201</v>
+      </c>
+      <c r="BY3" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="BZ3" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="CA3" s="18" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="BV3" s="17" t="s">
-        <v>134</v>
-      </c>
-      <c r="BW3" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="BX3" s="17">
-        <v>201</v>
-      </c>
-      <c r="BY3" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="BZ3" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="CA3" s="17" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="4" spans="1:92" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>77</v>
-      </c>
       <c r="E4" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>80</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="F4" s="8"/>
+      <c r="G4" s="11"/>
       <c r="H4" s="11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K4" s="12">
         <v>45597</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M4" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N4" s="10">
         <v>1</v>
@@ -2788,53 +1994,53 @@
         <v>213111231</v>
       </c>
       <c r="P4" s="11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q4" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="R4" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="R4" s="11" t="s">
-        <v>85</v>
-      </c>
       <c r="S4" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T4" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U4" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="V4" s="14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="W4" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X4" s="12">
         <f t="shared" si="0"/>
         <v>45597</v>
       </c>
       <c r="Y4" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Z4" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AA4" s="8" t="s">
         <v>138</v>
       </c>
       <c r="AB4" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AC4" s="8" t="s">
         <v>139</v>
       </c>
       <c r="AD4" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AE4" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF4" s="8" t="s">
         <v>140</v>
@@ -2847,10 +2053,10 @@
         <v>45962</v>
       </c>
       <c r="AI4" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AJ4" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK4" s="12">
         <f t="shared" si="1"/>
@@ -2865,7 +2071,7 @@
         <v>45597</v>
       </c>
       <c r="AN4" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO4" s="8" t="s">
         <v>141</v>
@@ -2878,64 +2084,64 @@
         <v>45687</v>
       </c>
       <c r="AR4" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AS4" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="AT4" s="10">
-        <v>9661113836</v>
+        <v>104</v>
+      </c>
+      <c r="AT4" s="17">
+        <v>9661111966</v>
       </c>
       <c r="AU4" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AV4" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="AW4" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AX4" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="AY4" s="17">
+        <v>144022795</v>
+      </c>
+      <c r="AZ4" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="AW4" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="AX4" s="16" t="s">
+      <c r="BA4" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="AY4" s="10">
-        <v>144822715</v>
-      </c>
-      <c r="AZ4" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="BA4" s="12" t="s">
-        <v>105</v>
-      </c>
       <c r="BB4" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="BC4" s="12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BD4" s="16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="BE4" s="16" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BF4" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BG4" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BH4" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BI4" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BJ4" s="16" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BK4" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="BL4" s="13" t="s">
         <v>142</v>
@@ -2944,13 +2150,13 @@
         <v>143</v>
       </c>
       <c r="BN4" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BO4" s="13">
         <v>1991</v>
       </c>
       <c r="BP4" s="13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BQ4" s="13">
         <v>1989</v>
@@ -2962,67 +2168,61 @@
         <v>144</v>
       </c>
       <c r="BT4" s="13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BU4" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="BV4" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="BV4" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="BW4" s="17" t="s">
+      <c r="BW4" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="BX4" s="17">
+      <c r="BX4" s="18">
         <v>213</v>
       </c>
-      <c r="BY4" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="BZ4" s="17" t="s">
+      <c r="BY4" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="CA4" s="17" t="s">
+      <c r="BZ4" s="18" t="s">
         <v>125</v>
       </c>
+      <c r="CA4" s="18" t="s">
+        <v>126</v>
+      </c>
     </row>
-    <row r="5" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8" t="s">
+    <row r="5" ht="15.6" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>127</v>
-      </c>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
       <c r="D5" s="9" t="s">
         <v>128</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>80</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="F5" s="8"/>
+      <c r="G5" s="11"/>
       <c r="H5" s="11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K5" s="12">
         <v>45597</v>
       </c>
       <c r="L5" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M5" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N5" s="10">
         <v>1</v>
@@ -3031,56 +2231,56 @@
         <v>213111231</v>
       </c>
       <c r="P5" s="11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q5" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="R5" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="R5" s="11" t="s">
-        <v>85</v>
-      </c>
       <c r="S5" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T5" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U5" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="V5" s="14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="W5" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X5" s="12">
         <f t="shared" si="0"/>
         <v>45597</v>
       </c>
       <c r="Y5" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Z5" s="11" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AA5" s="8" t="s">
         <v>138</v>
       </c>
       <c r="AB5" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AC5" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AD5" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AE5" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF5" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG5" s="15">
         <v>40</v>
@@ -3090,10 +2290,10 @@
         <v>45962</v>
       </c>
       <c r="AI5" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AJ5" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK5" s="12">
         <f t="shared" si="1"/>
@@ -3108,10 +2308,10 @@
         <v>45597</v>
       </c>
       <c r="AN5" s="11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AO5" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AP5" s="10">
         <v>100</v>
@@ -3121,79 +2321,79 @@
         <v>45687</v>
       </c>
       <c r="AR5" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AS5" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="AT5" s="10">
-        <v>9661118060</v>
+        <v>104</v>
+      </c>
+      <c r="AT5" s="17">
+        <v>9661118016</v>
       </c>
       <c r="AU5" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AV5" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="AW5" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AX5" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="AY5" s="17">
+        <v>144012796</v>
+      </c>
+      <c r="AZ5" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="AW5" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="AX5" s="16" t="s">
+      <c r="BA5" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="AY5" s="10">
-        <v>144812716</v>
-      </c>
-      <c r="AZ5" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="BA5" s="12" t="s">
-        <v>105</v>
-      </c>
       <c r="BB5" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="BC5" s="12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BD5" s="16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="BE5" s="16" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BF5" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BG5" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BH5" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BI5" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BJ5" s="16" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BK5" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="BL5" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="BM5" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="BM5" s="13" t="s">
-        <v>152</v>
-      </c>
       <c r="BN5" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BO5" s="13">
         <v>2024</v>
       </c>
       <c r="BP5" s="13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BQ5" s="13">
         <v>2021</v>
@@ -3202,70 +2402,64 @@
         <v>2024</v>
       </c>
       <c r="BS5" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="BT5" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="BU5" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="BV5" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="BT5" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="BU5" s="13" t="s">
+      <c r="BW5" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="BX5" s="18">
+        <v>207</v>
+      </c>
+      <c r="BY5" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="BZ5" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="CA5" s="18" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="6" ht="15.6" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="BV5" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="BW5" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="BX5" s="17">
-        <v>207</v>
-      </c>
-      <c r="BY5" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="BZ5" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="CA5" s="17" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="6" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>77</v>
-      </c>
       <c r="E6" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>80</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="F6" s="8"/>
+      <c r="G6" s="11"/>
       <c r="H6" s="11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K6" s="12">
         <v>45597</v>
       </c>
       <c r="L6" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M6" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N6" s="10">
         <v>1</v>
@@ -3274,56 +2468,56 @@
         <v>213111231</v>
       </c>
       <c r="P6" s="11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q6" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="R6" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="R6" s="11" t="s">
-        <v>85</v>
-      </c>
       <c r="S6" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T6" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U6" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="V6" s="14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="W6" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X6" s="12">
         <f t="shared" si="0"/>
         <v>45597</v>
       </c>
       <c r="Y6" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Z6" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AA6" s="8" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AB6" s="8" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="AC6" s="8" t="s">
         <v>139</v>
       </c>
       <c r="AD6" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AE6" s="10" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="AF6" s="8" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="AG6" s="15">
         <v>16</v>
@@ -3333,10 +2527,10 @@
         <v>45962</v>
       </c>
       <c r="AI6" s="11" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AJ6" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK6" s="12">
         <f t="shared" si="1"/>
@@ -3351,10 +2545,10 @@
         <v>45597</v>
       </c>
       <c r="AN6" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO6" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="AP6" s="10">
         <v>100</v>
@@ -3364,79 +2558,79 @@
         <v>45687</v>
       </c>
       <c r="AR6" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AS6" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="AT6" s="10">
-        <v>9661115728</v>
+        <v>104</v>
+      </c>
+      <c r="AT6" s="17">
+        <v>9661117114</v>
       </c>
       <c r="AU6" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AV6" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="AW6" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AX6" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="AY6" s="17">
+        <v>144002797</v>
+      </c>
+      <c r="AZ6" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="AW6" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="AX6" s="16" t="s">
+      <c r="BA6" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="AY6" s="10">
-        <v>144802717</v>
-      </c>
-      <c r="AZ6" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="BA6" s="12" t="s">
-        <v>105</v>
-      </c>
       <c r="BB6" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="BC6" s="12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BD6" s="16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="BE6" s="16" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BF6" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BG6" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BH6" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BI6" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BJ6" s="16" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BK6" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="BL6" s="13" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="BM6" s="13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="BN6" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BO6" s="13">
         <v>2000</v>
       </c>
       <c r="BP6" s="13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BQ6" s="13">
         <v>1995</v>
@@ -3445,70 +2639,64 @@
         <v>2000</v>
       </c>
       <c r="BS6" s="13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BT6" s="13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BU6" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="BV6" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="BV6" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="BW6" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="BX6" s="18">
+        <v>211</v>
+      </c>
+      <c r="BY6" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="BZ6" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="CA6" s="18" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="7" ht="15.6" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="BW6" s="17" t="s">
-        <v>165</v>
-      </c>
-      <c r="BX6" s="17">
-        <v>211</v>
-      </c>
-      <c r="BY6" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="BZ6" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="CA6" s="17" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="7" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>127</v>
-      </c>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
       <c r="D7" s="9" t="s">
         <v>128</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>80</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="F7" s="8"/>
+      <c r="G7" s="11"/>
       <c r="H7" s="11" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K7" s="12">
         <v>45597</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M7" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N7" s="10">
         <v>1</v>
@@ -3517,72 +2705,72 @@
         <v>213111231</v>
       </c>
       <c r="P7" s="11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q7" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="R7" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="R7" s="11" t="s">
-        <v>85</v>
-      </c>
       <c r="S7" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T7" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U7" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="V7" s="14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="W7" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X7" s="12">
         <f t="shared" si="0"/>
         <v>45597</v>
       </c>
       <c r="Y7" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Z7" s="11" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="AA7" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AB7" s="8" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="AC7" s="8" t="s">
         <v>139</v>
       </c>
       <c r="AD7" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AE7" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF7" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG7" s="15">
         <v>25</v>
       </c>
       <c r="AH7" s="12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AI7" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AJ7" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="AK7" s="12" t="str">
+        <v>101</v>
+      </c>
+      <c r="AK7" s="12">
         <f t="shared" si="1"/>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AL7" s="12">
         <f t="shared" si="2"/>
@@ -3593,10 +2781,10 @@
         <v>45597</v>
       </c>
       <c r="AN7" s="11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AO7" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AP7" s="10">
         <v>100</v>
@@ -3606,79 +2794,79 @@
         <v>45687</v>
       </c>
       <c r="AR7" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AS7" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="AT7" s="10">
-        <v>9661116190</v>
+        <v>104</v>
+      </c>
+      <c r="AT7" s="17">
+        <v>9661119545</v>
       </c>
       <c r="AU7" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AV7" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="AW7" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AX7" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="AY7" s="17">
+        <v>143992798</v>
+      </c>
+      <c r="AZ7" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="AW7" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="AX7" s="16" t="s">
+      <c r="BA7" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="AY7" s="10">
-        <v>144792718</v>
-      </c>
-      <c r="AZ7" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="BA7" s="12" t="s">
-        <v>105</v>
-      </c>
       <c r="BB7" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="BC7" s="12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BD7" s="16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="BE7" s="16" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BF7" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BG7" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BH7" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BI7" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BJ7" s="16" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BK7" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="BL7" s="13" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="BM7" s="13" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="BN7" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BO7" s="13">
         <v>2000</v>
       </c>
       <c r="BP7" s="13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BQ7" s="13">
         <v>1995</v>
@@ -3687,70 +2875,64 @@
         <v>2000</v>
       </c>
       <c r="BS7" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="BT7" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="BU7" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="BV7" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="BW7" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="BX7" s="18">
+        <v>211</v>
+      </c>
+      <c r="BY7" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="BZ7" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="CA7" s="18" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="8" ht="15.6" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="BT7" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="BU7" s="13" t="s">
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="BV7" s="17" t="s">
+      <c r="E8" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="F8" s="8"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="BW7" s="17" t="s">
-        <v>175</v>
-      </c>
-      <c r="BX7" s="17">
-        <v>211</v>
-      </c>
-      <c r="BY7" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="BZ7" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="CA7" s="17" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="8" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="H8" s="11" t="s">
-        <v>178</v>
-      </c>
       <c r="I8" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K8" s="12">
         <v>45597</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N8" s="10">
         <v>1</v>
@@ -3759,56 +2941,56 @@
         <v>213111231</v>
       </c>
       <c r="P8" s="11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q8" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="R8" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="R8" s="11" t="s">
-        <v>85</v>
-      </c>
       <c r="S8" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T8" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U8" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="V8" s="14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="W8" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X8" s="12">
         <f t="shared" si="0"/>
         <v>45597</v>
       </c>
       <c r="Y8" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Z8" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AA8" s="8" t="s">
         <v>138</v>
       </c>
       <c r="AB8" s="8" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="AC8" s="8" t="s">
         <v>139</v>
       </c>
       <c r="AD8" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AE8" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF8" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG8" s="15">
         <v>30</v>
@@ -3818,10 +3000,10 @@
         <v>45962</v>
       </c>
       <c r="AI8" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AJ8" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK8" s="12">
         <f t="shared" si="1"/>
@@ -3836,10 +3018,10 @@
         <v>45597</v>
       </c>
       <c r="AN8" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO8" s="8" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="AP8" s="10">
         <v>100</v>
@@ -3849,79 +3031,79 @@
         <v>45687</v>
       </c>
       <c r="AR8" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AS8" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="AT8" s="10">
-        <v>9661118247</v>
+        <v>104</v>
+      </c>
+      <c r="AT8" s="17">
+        <v>9661111867</v>
       </c>
       <c r="AU8" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AV8" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="AW8" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AX8" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="AY8" s="17">
+        <v>143982799</v>
+      </c>
+      <c r="AZ8" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="AW8" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="AX8" s="16" t="s">
+      <c r="BA8" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="AY8" s="10">
-        <v>144782719</v>
-      </c>
-      <c r="AZ8" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="BA8" s="12" t="s">
-        <v>105</v>
-      </c>
       <c r="BB8" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="BC8" s="12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BD8" s="16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="BE8" s="16" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BF8" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BG8" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BH8" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BI8" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BJ8" s="16" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BK8" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="BL8" s="13" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="BM8" s="13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="BN8" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BO8" s="13">
         <v>2000</v>
       </c>
       <c r="BP8" s="13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BQ8" s="13">
         <v>1995</v>
@@ -3930,70 +3112,64 @@
         <v>2000</v>
       </c>
       <c r="BS8" s="13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BT8" s="13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BU8" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="BV8" s="17" t="s">
-        <v>181</v>
-      </c>
-      <c r="BW8" s="17" t="s">
-        <v>182</v>
-      </c>
-      <c r="BX8" s="17">
+        <v>79</v>
+      </c>
+      <c r="BV8" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="BW8" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="BX8" s="18">
         <v>213</v>
       </c>
-      <c r="BY8" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="BZ8" s="17" t="s">
+      <c r="BY8" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="CA8" s="17" t="s">
+      <c r="BZ8" s="18" t="s">
         <v>125</v>
       </c>
+      <c r="CA8" s="18" t="s">
+        <v>126</v>
+      </c>
     </row>
-    <row r="9" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>127</v>
-      </c>
+    <row r="9" ht="15.6" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
       <c r="D9" s="9" t="s">
         <v>128</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>80</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="F9" s="8"/>
+      <c r="G9" s="11"/>
       <c r="H9" s="11" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K9" s="12">
         <v>45597</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N9" s="10">
         <v>1</v>
@@ -4002,56 +3178,56 @@
         <v>213111231</v>
       </c>
       <c r="P9" s="11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q9" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="R9" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="R9" s="11" t="s">
-        <v>85</v>
-      </c>
       <c r="S9" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T9" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U9" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="V9" s="14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="W9" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X9" s="12">
         <f t="shared" si="0"/>
         <v>45597</v>
       </c>
       <c r="Y9" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Z9" s="11" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="AA9" s="8" t="s">
         <v>138</v>
       </c>
       <c r="AB9" s="8" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="AC9" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AD9" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AE9" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF9" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG9" s="15">
         <v>40</v>
@@ -4061,10 +3237,10 @@
         <v>45962</v>
       </c>
       <c r="AI9" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AJ9" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK9" s="12">
         <f t="shared" si="1"/>
@@ -4079,10 +3255,10 @@
         <v>45597</v>
       </c>
       <c r="AN9" s="11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AO9" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AP9" s="10">
         <v>100</v>
@@ -4092,64 +3268,64 @@
         <v>45687</v>
       </c>
       <c r="AR9" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AS9" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="AT9" s="10">
-        <v>9661110316</v>
+        <v>104</v>
+      </c>
+      <c r="AT9" s="17">
+        <v>9661116828</v>
       </c>
       <c r="AU9" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AV9" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="AW9" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AX9" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="AY9" s="17">
+        <v>143972800</v>
+      </c>
+      <c r="AZ9" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="AW9" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="AX9" s="16" t="s">
+      <c r="BA9" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="AY9" s="10">
-        <v>144772720</v>
-      </c>
-      <c r="AZ9" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="BA9" s="12" t="s">
-        <v>105</v>
-      </c>
       <c r="BB9" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="BC9" s="12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BD9" s="16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="BE9" s="16" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BF9" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BG9" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BH9" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BI9" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BJ9" s="16" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BK9" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="BL9" s="13" t="s">
         <v>142</v>
@@ -4158,13 +3334,13 @@
         <v>143</v>
       </c>
       <c r="BN9" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BO9" s="13">
         <v>1991</v>
       </c>
       <c r="BP9" s="13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BQ9" s="13">
         <v>1989</v>
@@ -4176,67 +3352,61 @@
         <v>144</v>
       </c>
       <c r="BT9" s="13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BU9" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="BV9" s="18" t="s">
+        <v>183</v>
+      </c>
+      <c r="BW9" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="BX9" s="18">
+        <v>211</v>
+      </c>
+      <c r="BY9" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="BZ9" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="CA9" s="18" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="10" ht="15.6" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="BV9" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="BW9" s="17" t="s">
-        <v>189</v>
-      </c>
-      <c r="BX9" s="17">
-        <v>211</v>
-      </c>
-      <c r="BY9" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="BZ9" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="CA9" s="17" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="10" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>77</v>
-      </c>
       <c r="E10" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>80</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="F10" s="8"/>
+      <c r="G10" s="11"/>
       <c r="H10" s="11" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K10" s="12">
         <v>45597</v>
       </c>
       <c r="L10" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N10" s="10">
         <v>1</v>
@@ -4245,53 +3415,53 @@
         <v>213111231</v>
       </c>
       <c r="P10" s="11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q10" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="R10" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="R10" s="11" t="s">
-        <v>85</v>
-      </c>
       <c r="S10" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T10" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U10" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="V10" s="14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="W10" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X10" s="12">
         <f t="shared" si="0"/>
         <v>45597</v>
       </c>
       <c r="Y10" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Z10" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AA10" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AB10" s="8" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="AC10" s="8" t="s">
         <v>139</v>
       </c>
       <c r="AD10" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AE10" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF10" s="8" t="s">
         <v>140</v>
@@ -4300,17 +3470,17 @@
         <v>20</v>
       </c>
       <c r="AH10" s="12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AI10" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AJ10" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="AK10" s="12" t="str">
+        <v>101</v>
+      </c>
+      <c r="AK10" s="12">
         <f t="shared" si="1"/>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AL10" s="12">
         <f t="shared" si="2"/>
@@ -4321,10 +3491,10 @@
         <v>45597</v>
       </c>
       <c r="AN10" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO10" s="8" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="AP10" s="10">
         <v>100</v>
@@ -4334,79 +3504,79 @@
         <v>45687</v>
       </c>
       <c r="AR10" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AS10" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="AT10" s="10">
-        <v>9661117774</v>
+        <v>104</v>
+      </c>
+      <c r="AT10" s="17">
+        <v>9661115607</v>
       </c>
       <c r="AU10" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AV10" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="AW10" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AX10" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="AY10" s="17">
+        <v>143962801</v>
+      </c>
+      <c r="AZ10" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="AW10" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="AX10" s="16" t="s">
+      <c r="BA10" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="AY10" s="10">
-        <v>144762721</v>
-      </c>
-      <c r="AZ10" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="BA10" s="12" t="s">
-        <v>105</v>
-      </c>
       <c r="BB10" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="BC10" s="12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BD10" s="16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="BE10" s="16" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BF10" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BG10" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BH10" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BI10" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BJ10" s="16" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BK10" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="BL10" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="BM10" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="BM10" s="13" t="s">
-        <v>152</v>
-      </c>
       <c r="BN10" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BO10" s="13">
         <v>2024</v>
       </c>
       <c r="BP10" s="13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BQ10" s="13">
         <v>2021</v>
@@ -4415,70 +3585,64 @@
         <v>2024</v>
       </c>
       <c r="BS10" s="13" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="BT10" s="13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BU10" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="BV10" s="17" t="s">
-        <v>194</v>
-      </c>
-      <c r="BW10" s="17" t="s">
-        <v>195</v>
-      </c>
-      <c r="BX10" s="17">
+        <v>79</v>
+      </c>
+      <c r="BV10" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="BW10" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="BX10" s="18">
         <v>213</v>
       </c>
-      <c r="BY10" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="BZ10" s="17" t="s">
+      <c r="BY10" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="CA10" s="17" t="s">
+      <c r="BZ10" s="18" t="s">
         <v>125</v>
       </c>
+      <c r="CA10" s="18" t="s">
+        <v>126</v>
+      </c>
     </row>
-    <row r="11" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>127</v>
-      </c>
+    <row r="11" ht="15.6" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
       <c r="D11" s="9" t="s">
         <v>128</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>80</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="F11" s="8"/>
+      <c r="G11" s="11"/>
       <c r="H11" s="11" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K11" s="12">
         <v>45597</v>
       </c>
       <c r="L11" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N11" s="10">
         <v>1</v>
@@ -4487,72 +3651,72 @@
         <v>213111231</v>
       </c>
       <c r="P11" s="11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q11" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="R11" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="R11" s="11" t="s">
-        <v>85</v>
-      </c>
       <c r="S11" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T11" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U11" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="V11" s="14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="W11" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X11" s="12">
         <f t="shared" si="0"/>
         <v>45597</v>
       </c>
       <c r="Y11" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Z11" s="11" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="AA11" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AB11" s="8" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="AC11" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AD11" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AE11" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF11" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG11" s="15">
         <v>40</v>
       </c>
       <c r="AH11" s="12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AI11" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AJ11" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="AK11" s="12" t="str">
+        <v>101</v>
+      </c>
+      <c r="AK11" s="12">
         <f t="shared" si="1"/>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AL11" s="12">
         <f t="shared" si="2"/>
@@ -4563,10 +3727,10 @@
         <v>45597</v>
       </c>
       <c r="AN11" s="11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AO11" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AP11" s="10">
         <v>100</v>
@@ -4576,79 +3740,79 @@
         <v>45687</v>
       </c>
       <c r="AR11" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AS11" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="AT11" s="10">
-        <v>9661115046</v>
+        <v>104</v>
+      </c>
+      <c r="AT11" s="17">
+        <v>9661119831</v>
       </c>
       <c r="AU11" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AV11" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="AW11" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AX11" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="AY11" s="17">
+        <v>143952802</v>
+      </c>
+      <c r="AZ11" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="AW11" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="AX11" s="16" t="s">
+      <c r="BA11" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="AY11" s="10">
-        <v>144752722</v>
-      </c>
-      <c r="AZ11" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="BA11" s="12" t="s">
-        <v>105</v>
-      </c>
       <c r="BB11" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="BC11" s="12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BD11" s="16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="BE11" s="16" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BF11" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BG11" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BH11" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BI11" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BJ11" s="16" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BK11" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="BL11" s="13" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="BM11" s="13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="BN11" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BO11" s="13">
         <v>2000</v>
       </c>
       <c r="BP11" s="13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BQ11" s="13">
         <v>1995</v>
@@ -4657,70 +3821,64 @@
         <v>2000</v>
       </c>
       <c r="BS11" s="13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BT11" s="13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BU11" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="BV11" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="BW11" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="BX11" s="18">
+        <v>201</v>
+      </c>
+      <c r="BY11" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="BZ11" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="CA11" s="18" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="12" ht="15.6" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="BV11" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="BW11" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="BX11" s="17">
-        <v>201</v>
-      </c>
-      <c r="BY11" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="BZ11" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="CA11" s="17" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="12" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>77</v>
-      </c>
       <c r="E12" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>80</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="F12" s="8"/>
+      <c r="G12" s="11"/>
       <c r="H12" s="11" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K12" s="12">
         <v>45597</v>
       </c>
       <c r="L12" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N12" s="10">
         <v>1</v>
@@ -4729,56 +3887,56 @@
         <v>213111231</v>
       </c>
       <c r="P12" s="11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q12" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="R12" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="R12" s="11" t="s">
-        <v>85</v>
-      </c>
       <c r="S12" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T12" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U12" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="V12" s="14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="W12" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X12" s="12">
         <f t="shared" si="0"/>
         <v>45597</v>
       </c>
       <c r="Y12" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Z12" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AA12" s="8" t="s">
         <v>138</v>
       </c>
       <c r="AB12" s="8" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="AC12" s="8" t="s">
         <v>139</v>
       </c>
       <c r="AD12" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AE12" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF12" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG12" s="15">
         <v>25</v>
@@ -4788,10 +3946,10 @@
         <v>45962</v>
       </c>
       <c r="AI12" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AJ12" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK12" s="12">
         <f t="shared" si="1"/>
@@ -4806,10 +3964,10 @@
         <v>45597</v>
       </c>
       <c r="AN12" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO12" s="8" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="AP12" s="10">
         <v>100</v>
@@ -4819,79 +3977,79 @@
         <v>45687</v>
       </c>
       <c r="AR12" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AS12" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="AT12" s="10">
-        <v>9661115189</v>
+        <v>104</v>
+      </c>
+      <c r="AT12" s="17">
+        <v>9661114287</v>
       </c>
       <c r="AU12" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AV12" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="AW12" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AX12" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="AY12" s="17">
+        <v>143942803</v>
+      </c>
+      <c r="AZ12" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="AW12" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="AX12" s="16" t="s">
+      <c r="BA12" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="AY12" s="10">
-        <v>144742723</v>
-      </c>
-      <c r="AZ12" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="BA12" s="12" t="s">
-        <v>105</v>
-      </c>
       <c r="BB12" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="BC12" s="12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BD12" s="16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="BE12" s="16" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BF12" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BG12" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BH12" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BI12" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BJ12" s="16" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BK12" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="BL12" s="13" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="BM12" s="13" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="BN12" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BO12" s="13">
         <v>2000</v>
       </c>
       <c r="BP12" s="13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BQ12" s="13">
         <v>1995</v>
@@ -4900,70 +4058,64 @@
         <v>2000</v>
       </c>
       <c r="BS12" s="13" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="BT12" s="13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BU12" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="BV12" s="17" t="s">
-        <v>208</v>
-      </c>
-      <c r="BW12" s="17" t="s">
-        <v>209</v>
-      </c>
-      <c r="BX12" s="17">
+        <v>79</v>
+      </c>
+      <c r="BV12" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="BW12" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="BX12" s="18">
         <v>213</v>
       </c>
-      <c r="BY12" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="BZ12" s="17" t="s">
+      <c r="BY12" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="CA12" s="17" t="s">
+      <c r="BZ12" s="18" t="s">
         <v>125</v>
       </c>
+      <c r="CA12" s="18" t="s">
+        <v>126</v>
+      </c>
     </row>
-    <row r="13" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>127</v>
-      </c>
+    <row r="13" ht="15.6" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
       <c r="D13" s="9" t="s">
         <v>128</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>80</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="F13" s="8"/>
+      <c r="G13" s="11"/>
       <c r="H13" s="11" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K13" s="12">
         <v>45597</v>
       </c>
       <c r="L13" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N13" s="10">
         <v>1</v>
@@ -4972,56 +4124,56 @@
         <v>213111231</v>
       </c>
       <c r="P13" s="11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q13" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="R13" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="R13" s="11" t="s">
-        <v>85</v>
-      </c>
       <c r="S13" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T13" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U13" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="V13" s="14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="W13" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X13" s="12">
         <f t="shared" si="0"/>
         <v>45597</v>
       </c>
       <c r="Y13" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Z13" s="11" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="AA13" s="8" t="s">
         <v>138</v>
       </c>
       <c r="AB13" s="8" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="AC13" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AD13" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AE13" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF13" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG13" s="15">
         <v>40</v>
@@ -5031,10 +4183,10 @@
         <v>45962</v>
       </c>
       <c r="AI13" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AJ13" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK13" s="12">
         <f t="shared" si="1"/>
@@ -5049,10 +4201,10 @@
         <v>45597</v>
       </c>
       <c r="AN13" s="11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AO13" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AP13" s="10">
         <v>100</v>
@@ -5062,79 +4214,79 @@
         <v>45687</v>
       </c>
       <c r="AR13" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AS13" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="AT13" s="10">
-        <v>9661116498</v>
+        <v>104</v>
+      </c>
+      <c r="AT13" s="17">
+        <v>9661119556</v>
       </c>
       <c r="AU13" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AV13" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="AW13" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AX13" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="AY13" s="17">
+        <v>143932804</v>
+      </c>
+      <c r="AZ13" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="AW13" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="AX13" s="16" t="s">
+      <c r="BA13" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="AY13" s="10">
-        <v>144732724</v>
-      </c>
-      <c r="AZ13" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="BA13" s="12" t="s">
-        <v>105</v>
-      </c>
       <c r="BB13" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="BC13" s="12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BD13" s="16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="BE13" s="16" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BF13" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BG13" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BH13" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BI13" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BJ13" s="16" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BK13" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="BL13" s="13" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="BM13" s="13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="BN13" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BO13" s="13">
         <v>2000</v>
       </c>
       <c r="BP13" s="13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BQ13" s="13">
         <v>1995</v>
@@ -5143,70 +4295,64 @@
         <v>2000</v>
       </c>
       <c r="BS13" s="13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BT13" s="13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BU13" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="BV13" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="BW13" s="18" t="s">
+        <v>207</v>
+      </c>
+      <c r="BX13" s="18">
+        <v>209</v>
+      </c>
+      <c r="BY13" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="BZ13" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="CA13" s="18" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="14" ht="15.6" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="BV13" s="17" t="s">
-        <v>215</v>
-      </c>
-      <c r="BW13" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="BX13" s="17">
+      <c r="E14" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="F14" s="8"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="BY13" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="BZ13" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="CA13" s="17" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="14" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="H14" s="11" t="s">
-        <v>219</v>
-      </c>
       <c r="I14" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K14" s="12">
         <v>45597</v>
       </c>
       <c r="L14" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N14" s="10">
         <v>1</v>
@@ -5215,53 +4361,53 @@
         <v>213111231</v>
       </c>
       <c r="P14" s="11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q14" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="R14" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="R14" s="11" t="s">
-        <v>85</v>
-      </c>
       <c r="S14" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T14" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U14" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="V14" s="14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="W14" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X14" s="12">
         <f t="shared" si="0"/>
         <v>45597</v>
       </c>
       <c r="Y14" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Z14" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AA14" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AB14" s="8" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="AC14" s="8" t="s">
         <v>139</v>
       </c>
       <c r="AD14" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AE14" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF14" s="8" t="s">
         <v>140</v>
@@ -5270,17 +4416,17 @@
         <v>24</v>
       </c>
       <c r="AH14" s="12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AI14" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AJ14" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="AK14" s="12" t="str">
+        <v>101</v>
+      </c>
+      <c r="AK14" s="12">
         <f t="shared" si="1"/>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AL14" s="12">
         <f t="shared" si="2"/>
@@ -5291,10 +4437,10 @@
         <v>45597</v>
       </c>
       <c r="AN14" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO14" s="8" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AP14" s="10">
         <v>100</v>
@@ -5304,64 +4450,64 @@
         <v>45687</v>
       </c>
       <c r="AR14" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AS14" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="AT14" s="10">
-        <v>9661118324</v>
+        <v>104</v>
+      </c>
+      <c r="AT14" s="17">
+        <v>9661115585</v>
       </c>
       <c r="AU14" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AV14" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="AW14" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AX14" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="AY14" s="17">
+        <v>143922805</v>
+      </c>
+      <c r="AZ14" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="AW14" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="AX14" s="16" t="s">
+      <c r="BA14" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="AY14" s="10">
-        <v>144722725</v>
-      </c>
-      <c r="AZ14" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="BA14" s="12" t="s">
-        <v>105</v>
-      </c>
       <c r="BB14" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="BC14" s="12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BD14" s="16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="BE14" s="16" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BF14" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BG14" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BH14" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BI14" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BJ14" s="16" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BK14" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="BL14" s="13" t="s">
         <v>142</v>
@@ -5370,13 +4516,13 @@
         <v>143</v>
       </c>
       <c r="BN14" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BO14" s="13">
         <v>1991</v>
       </c>
       <c r="BP14" s="13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BQ14" s="13">
         <v>1989</v>
@@ -5388,67 +4534,61 @@
         <v>144</v>
       </c>
       <c r="BT14" s="13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BU14" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="BV14" s="18" t="s">
+        <v>211</v>
+      </c>
+      <c r="BW14" s="18" t="s">
+        <v>212</v>
+      </c>
+      <c r="BX14" s="18">
+        <v>211</v>
+      </c>
+      <c r="BY14" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="BZ14" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="CA14" s="18" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="15" ht="15.6" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="BV14" s="17" t="s">
-        <v>221</v>
-      </c>
-      <c r="BW14" s="17" t="s">
-        <v>222</v>
-      </c>
-      <c r="BX14" s="17">
-        <v>211</v>
-      </c>
-      <c r="BY14" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="BZ14" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="CA14" s="17" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="15" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>77</v>
-      </c>
       <c r="E15" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>80</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="F15" s="8"/>
+      <c r="G15" s="11"/>
       <c r="H15" s="11" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J15" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K15" s="12">
         <v>45597</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N15" s="10">
         <v>1</v>
@@ -5457,56 +4597,56 @@
         <v>213111231</v>
       </c>
       <c r="P15" s="11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q15" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="R15" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="R15" s="11" t="s">
-        <v>85</v>
-      </c>
       <c r="S15" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T15" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U15" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="V15" s="14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="W15" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X15" s="12">
         <f t="shared" si="0"/>
         <v>45597</v>
       </c>
       <c r="Y15" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Z15" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AA15" s="8" t="s">
         <v>138</v>
       </c>
       <c r="AB15" s="8" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="AC15" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AD15" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AE15" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF15" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG15" s="15">
         <v>40</v>
@@ -5516,10 +4656,10 @@
         <v>45962</v>
       </c>
       <c r="AI15" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AJ15" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK15" s="12">
         <f t="shared" si="1"/>
@@ -5534,10 +4674,10 @@
         <v>45597</v>
       </c>
       <c r="AN15" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO15" s="8" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="AP15" s="10">
         <v>100</v>
@@ -5547,79 +4687,79 @@
         <v>45687</v>
       </c>
       <c r="AR15" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AS15" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="AT15" s="10">
-        <v>9661117752</v>
+        <v>104</v>
+      </c>
+      <c r="AT15" s="17">
+        <v>9661116652</v>
       </c>
       <c r="AU15" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AV15" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="AW15" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AX15" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="AY15" s="17">
+        <v>143912806</v>
+      </c>
+      <c r="AZ15" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="AW15" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="AX15" s="16" t="s">
+      <c r="BA15" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="AY15" s="10">
-        <v>144712726</v>
-      </c>
-      <c r="AZ15" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="BA15" s="12" t="s">
-        <v>105</v>
-      </c>
       <c r="BB15" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="BC15" s="12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BD15" s="16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="BE15" s="16" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BF15" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BG15" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BH15" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BI15" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BJ15" s="16" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BK15" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="BL15" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="BM15" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="BM15" s="13" t="s">
-        <v>152</v>
-      </c>
       <c r="BN15" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BO15" s="13">
         <v>2024</v>
       </c>
       <c r="BP15" s="13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BQ15" s="13">
         <v>2021</v>
@@ -5628,70 +4768,64 @@
         <v>2024</v>
       </c>
       <c r="BS15" s="13" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="BT15" s="13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BU15" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="BV15" s="18" t="s">
+        <v>215</v>
+      </c>
+      <c r="BW15" s="18" t="s">
+        <v>216</v>
+      </c>
+      <c r="BX15" s="18">
+        <v>213</v>
+      </c>
+      <c r="BY15" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="BZ15" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="CA15" s="18" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="16" ht="15.6" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="BV15" s="17" t="s">
-        <v>226</v>
-      </c>
-      <c r="BW15" s="17" t="s">
-        <v>227</v>
-      </c>
-      <c r="BX15" s="17">
-        <v>213</v>
-      </c>
-      <c r="BY15" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="BZ15" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="CA15" s="17" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="16" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>77</v>
-      </c>
       <c r="E16" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="G16" s="11" t="s">
-        <v>80</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="F16" s="8"/>
+      <c r="G16" s="11"/>
       <c r="H16" s="11" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K16" s="12">
         <v>45597</v>
       </c>
       <c r="L16" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N16" s="10">
         <v>1</v>
@@ -5700,72 +4834,72 @@
         <v>213111231</v>
       </c>
       <c r="P16" s="11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q16" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="R16" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="R16" s="11" t="s">
-        <v>85</v>
-      </c>
       <c r="S16" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T16" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U16" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="V16" s="14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="W16" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X16" s="12">
         <f t="shared" si="0"/>
         <v>45597</v>
       </c>
       <c r="Y16" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Z16" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AA16" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AB16" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AC16" s="8" t="s">
         <v>139</v>
       </c>
       <c r="AD16" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AE16" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF16" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG16" s="15">
         <v>30</v>
       </c>
       <c r="AH16" s="12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AI16" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AJ16" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="AK16" s="12" t="str">
+        <v>101</v>
+      </c>
+      <c r="AK16" s="12">
         <f t="shared" si="1"/>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AL16" s="12">
         <f t="shared" si="2"/>
@@ -5776,10 +4910,10 @@
         <v>45597</v>
       </c>
       <c r="AN16" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO16" s="8" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="AP16" s="10">
         <v>100</v>
@@ -5789,79 +4923,79 @@
         <v>45687</v>
       </c>
       <c r="AR16" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AS16" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="AT16" s="10">
-        <v>9661116168</v>
+        <v>104</v>
+      </c>
+      <c r="AT16" s="17">
+        <v>9661111845</v>
       </c>
       <c r="AU16" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AV16" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="AW16" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AX16" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="AY16" s="17">
+        <v>143902807</v>
+      </c>
+      <c r="AZ16" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="AW16" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="AX16" s="16" t="s">
+      <c r="BA16" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="AY16" s="10">
-        <v>144702727</v>
-      </c>
-      <c r="AZ16" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="BA16" s="12" t="s">
-        <v>105</v>
-      </c>
       <c r="BB16" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="BC16" s="12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BD16" s="16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="BE16" s="16" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BF16" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BG16" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BH16" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BI16" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BJ16" s="16" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BK16" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="BL16" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="BM16" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="BM16" s="13" t="s">
-        <v>152</v>
-      </c>
       <c r="BN16" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BO16" s="13">
         <v>2024</v>
       </c>
       <c r="BP16" s="13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BQ16" s="13">
         <v>2021</v>
@@ -5870,53 +5004,81 @@
         <v>2024</v>
       </c>
       <c r="BS16" s="13" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="BT16" s="13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BU16" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="BV16" s="17" t="s">
-        <v>231</v>
-      </c>
-      <c r="BW16" s="17" t="s">
-        <v>232</v>
-      </c>
-      <c r="BX16" s="17">
+        <v>79</v>
+      </c>
+      <c r="BV16" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="BW16" s="18" t="s">
+        <v>220</v>
+      </c>
+      <c r="BX16" s="18">
         <v>211</v>
       </c>
-      <c r="BY16" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="BZ16" s="17" t="s">
+      <c r="BY16" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="CA16" s="17" t="s">
+      <c r="BZ16" s="18" t="s">
         <v>125</v>
       </c>
+      <c r="CA16" s="18" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="17" ht="15.6" customHeight="1" spans="46:51" x14ac:dyDescent="0.25">
+      <c r="AT17" s="19"/>
+      <c r="AY17" s="19"/>
     </row>
   </sheetData>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ10:AJ16 Y10:Y16 W10:W16 T10:T16" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="12">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ10:AJ16">
       <formula1>INDIRECT($D1)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ2:AJ16 Y2:Y16 W2:W16 T2:T16" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ2:AJ16">
       <formula1>INDIRECT($D1)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH10:BH16 J10:J16" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH10:BH16">
       <formula1>INDIRECT($D2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH2:BH16 J2:J16" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH2:BH16">
       <formula1>INDIRECT($D2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J10:J16">
+      <formula1>INDIRECT($D2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J16">
+      <formula1>INDIRECT($D2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T10:T16">
+      <formula1>INDIRECT($D1)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T16">
+      <formula1>INDIRECT($D1)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W10:W16">
+      <formula1>INDIRECT($D1)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W16">
+      <formula1>INDIRECT($D1)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y10:Y16">
+      <formula1>INDIRECT($D1)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Y16">
+      <formula1>INDIRECT($D1)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="V2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="V3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="V2" r:id="rId1"/>
+    <hyperlink ref="V3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="0"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="0" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/Data/testDataCzechia_PK14.xlsx
+++ b/Data/testDataCzechia_PK14.xlsx
@@ -1,20 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2B4CE2D-E0E4-4AB0-BB51-210729A79273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176"/>
+    <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="2" name="Sheet1" state="visible" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1016" uniqueCount="249">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -244,247 +258,268 @@
     <t>Test1</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'Olaf Bartell' Employee:{undefined}TimeoutError: page.goto: Timeout 30000ms exceeded.
-Call log:
-  [2m- navigating to "https://wd3-impl.workday.com/wday/authgwy/primark14/login.htmld", waiting until "load"[22m
-</t>
+    <t>10697370</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>895 Retail Team 1 (Jaziz Wezupa (10573442) (Inherited))</t>
+  </si>
+  <si>
+    <t>Czechia</t>
+  </si>
+  <si>
+    <t>CzOne</t>
+  </si>
+  <si>
+    <t>TwentyFiveMarchThreeD</t>
+  </si>
+  <si>
+    <t>770 272 784</t>
+  </si>
+  <si>
+    <t>Mobile</t>
+  </si>
+  <si>
+    <t>Home</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>Prague</t>
+  </si>
+  <si>
+    <t>26401</t>
+  </si>
+  <si>
+    <t>Pardubic</t>
+  </si>
+  <si>
+    <t>Street Address</t>
+  </si>
+  <si>
+    <t>Test@primark.com</t>
+  </si>
+  <si>
+    <t>New Hire</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>Retail Assistant_NEW</t>
+  </si>
+  <si>
+    <t>Full time</t>
+  </si>
+  <si>
+    <t>895 Prague Wenceslas SQ</t>
+  </si>
+  <si>
+    <t>Salary</t>
+  </si>
+  <si>
+    <t>5 Days</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Employment Agreement</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>94 Retail Operatives</t>
+  </si>
+  <si>
+    <t>07 Footwear</t>
+  </si>
+  <si>
+    <t>Personal Number</t>
+  </si>
+  <si>
+    <t>11/11/1998</t>
+  </si>
+  <si>
+    <t>11/11/2055</t>
+  </si>
+  <si>
+    <t>Citizen ID Number</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>11/11/1996</t>
+  </si>
+  <si>
+    <t>Single (Czechia)</t>
+  </si>
+  <si>
+    <t>Citizen (Czechia)</t>
+  </si>
+  <si>
+    <t>Air Bank</t>
+  </si>
+  <si>
+    <t>Checking</t>
+  </si>
+  <si>
+    <t>AIRACZPPXXX</t>
+  </si>
+  <si>
+    <t>CZ6508000000192000145399</t>
+  </si>
+  <si>
+    <t>Bc</t>
+  </si>
+  <si>
+    <t>bakal</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Economics</t>
+  </si>
+  <si>
+    <t>2000.31130.00000000.6208R.2636</t>
+  </si>
+  <si>
+    <t>Maiden</t>
+  </si>
+  <si>
+    <t>Francis</t>
+  </si>
+  <si>
+    <t>Uzoho</t>
+  </si>
+  <si>
+    <t>Ne</t>
+  </si>
+  <si>
+    <t>Please select a Czech Republic Pay Group</t>
+  </si>
+  <si>
+    <t>CZ Monthly</t>
+  </si>
+  <si>
+    <t>Test2</t>
+  </si>
+  <si>
+    <t>10697371</t>
+  </si>
+  <si>
+    <t>895 Store Management (Jaziz Wezupa (10573442))</t>
+  </si>
+  <si>
+    <t>CzTwo</t>
+  </si>
+  <si>
+    <t>TwentyFiveMarchThree</t>
+  </si>
+  <si>
+    <t>Auto 27432012</t>
+  </si>
+  <si>
+    <t>Department Manager_NEW</t>
+  </si>
+  <si>
+    <t>92 Retail Management</t>
+  </si>
+  <si>
+    <t>251 Management Retail</t>
+  </si>
+  <si>
+    <t>Temitayo</t>
+  </si>
+  <si>
+    <t>Aina</t>
+  </si>
+  <si>
+    <t>Test3</t>
+  </si>
+  <si>
+    <t>10697372</t>
+  </si>
+  <si>
+    <t>CzThree</t>
+  </si>
+  <si>
+    <t>Fixed Term (Fixed Term)</t>
+  </si>
+  <si>
+    <t>Part time</t>
+  </si>
+  <si>
+    <t>4 Days</t>
+  </si>
+  <si>
+    <t>11 Household</t>
+  </si>
+  <si>
+    <t>Ing</t>
+  </si>
+  <si>
+    <t>magisters</t>
+  </si>
+  <si>
+    <t>1991.31150.62018000.00000.2636</t>
+  </si>
+  <si>
+    <t>Evans</t>
+  </si>
+  <si>
+    <t>Ogbonda</t>
+  </si>
+  <si>
+    <t>Test4</t>
+  </si>
+  <si>
+    <t>10697374</t>
+  </si>
+  <si>
+    <t>CzFour</t>
+  </si>
+  <si>
+    <t>Auto 21070719</t>
+  </si>
+  <si>
+    <t>Assistant Store Manager_NEW</t>
+  </si>
+  <si>
+    <t>PhDr</t>
+  </si>
+  <si>
+    <t>doktor</t>
+  </si>
+  <si>
+    <t>2024.26510.6208V097.P6208.4942</t>
+  </si>
+  <si>
+    <t>Imo</t>
+  </si>
+  <si>
+    <t>Obot</t>
+  </si>
+  <si>
+    <t>Test5</t>
+  </si>
+  <si>
+    <t>Test failed for 'CzFive TwentyFiveMarchThree' Employee: Errors and AlertsErrorPage Error- You have not entered an amount within the Compensation Guidelines.     (Employee Compensation Event For Hire Employee)AlertPage Alert- "Warning: You have entered an amount that is outside of the range or more than 10% higher than the current salary.  Please re-enter an amount inside the range, below 10% or continue and it will be sent for approval."     (Employee Compensation Event For Hire Employee) &amp; find failed Screenshot Path:-&gt;H:\Latest_Workday_Playwright/WorkdayFailedScreenshot/2025-03-02T20-46-46-860Z.png</t>
   </si>
   <si>
     <t>Failed</t>
   </si>
   <si>
-    <t>895 Retail Team 1 (Jaziz Wezupa (10573442) (Inherited))</t>
-  </si>
-  <si>
-    <t>Czechia</t>
-  </si>
-  <si>
-    <t>Olaf</t>
-  </si>
-  <si>
-    <t>Bartell</t>
-  </si>
-  <si>
-    <t>770 272 784</t>
-  </si>
-  <si>
-    <t>Mobile</t>
-  </si>
-  <si>
-    <t>Home</t>
-  </si>
-  <si>
-    <t>Test</t>
-  </si>
-  <si>
-    <t>Prague</t>
-  </si>
-  <si>
-    <t>26401</t>
-  </si>
-  <si>
-    <t>Pardubic</t>
-  </si>
-  <si>
-    <t>Street Address</t>
-  </si>
-  <si>
-    <t>Test@primark.com</t>
-  </si>
-  <si>
-    <t>New Hire</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Permanent</t>
-  </si>
-  <si>
-    <t>Retail Assistant_NEW</t>
-  </si>
-  <si>
-    <t>Full time</t>
-  </si>
-  <si>
-    <t>895 Prague Wenceslas SQ</t>
-  </si>
-  <si>
-    <t>Salary</t>
-  </si>
-  <si>
-    <t>5 Days</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Employment Agreement</t>
-  </si>
-  <si>
-    <t>Active</t>
-  </si>
-  <si>
-    <t>94 Retail Operatives</t>
-  </si>
-  <si>
-    <t>07 Footwear</t>
-  </si>
-  <si>
-    <t>Personal Number</t>
-  </si>
-  <si>
-    <t>11/11/1998</t>
-  </si>
-  <si>
-    <t>11/11/2055</t>
-  </si>
-  <si>
-    <t>Citizen ID Number</t>
-  </si>
-  <si>
-    <t>Female</t>
-  </si>
-  <si>
-    <t>11/11/1996</t>
-  </si>
-  <si>
-    <t>Single (Czechia)</t>
-  </si>
-  <si>
-    <t>Citizen (Czechia)</t>
-  </si>
-  <si>
-    <t>Air Bank</t>
-  </si>
-  <si>
-    <t>Checking</t>
-  </si>
-  <si>
-    <t>AIRACZPPXXX</t>
-  </si>
-  <si>
-    <t>CZ6508000000192000145399</t>
-  </si>
-  <si>
-    <t>Bc</t>
-  </si>
-  <si>
-    <t>bakal</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>Economics</t>
-  </si>
-  <si>
-    <t>2000.31130.00000000.6208R.2636</t>
-  </si>
-  <si>
-    <t>Maiden</t>
-  </si>
-  <si>
-    <t>Francis</t>
-  </si>
-  <si>
-    <t>Uzoho</t>
-  </si>
-  <si>
-    <t>Ne</t>
-  </si>
-  <si>
-    <t>Please select a Czech Republic Pay Group</t>
-  </si>
-  <si>
-    <t>CZ Monthly</t>
-  </si>
-  <si>
-    <t>Test2</t>
-  </si>
-  <si>
-    <t>895 Store Management (Jaziz Wezupa (10573442))</t>
-  </si>
-  <si>
-    <t>Verona</t>
-  </si>
-  <si>
-    <t>Wiza</t>
-  </si>
-  <si>
-    <t>Auto 48962562</t>
-  </si>
-  <si>
-    <t>Department Manager_NEW</t>
-  </si>
-  <si>
-    <t>92 Retail Management</t>
-  </si>
-  <si>
-    <t>251 Management Retail</t>
-  </si>
-  <si>
-    <t>Temitayo</t>
-  </si>
-  <si>
-    <t>Aina</t>
-  </si>
-  <si>
-    <t>Test3</t>
-  </si>
-  <si>
-    <t>Fixed Term (Fixed Term)</t>
-  </si>
-  <si>
-    <t>Part time</t>
-  </si>
-  <si>
-    <t>4 Days</t>
-  </si>
-  <si>
-    <t>11 Household</t>
-  </si>
-  <si>
-    <t>Ing</t>
-  </si>
-  <si>
-    <t>magisters</t>
-  </si>
-  <si>
-    <t>1991.31150.62018000.00000.2636</t>
-  </si>
-  <si>
-    <t>Evans</t>
-  </si>
-  <si>
-    <t>Ogbonda</t>
-  </si>
-  <si>
-    <t>Test4</t>
-  </si>
-  <si>
-    <t>Auto 73452255</t>
-  </si>
-  <si>
-    <t>Assistant Store Manager_NEW</t>
-  </si>
-  <si>
-    <t>PhDr</t>
-  </si>
-  <si>
-    <t>doktor</t>
-  </si>
-  <si>
-    <t>2024.26510.6208V097.P6208.4942</t>
-  </si>
-  <si>
-    <t>Imo</t>
-  </si>
-  <si>
-    <t>Obot</t>
-  </si>
-  <si>
-    <t>Test5</t>
+    <t>CzFive</t>
   </si>
   <si>
     <t>Students</t>
@@ -514,10 +549,16 @@
     <t>Test6</t>
   </si>
   <si>
+    <t>10697375</t>
+  </si>
+  <si>
+    <t>CzSix</t>
+  </si>
+  <si>
     <t>771 272 784</t>
   </si>
   <si>
-    <t>Auto 51256887</t>
+    <t>Auto 17265039</t>
   </si>
   <si>
     <t>In-Store Visual Merchandising Manager_NEW</t>
@@ -541,6 +582,12 @@
     <t>Test7</t>
   </si>
   <si>
+    <t>10697376</t>
+  </si>
+  <si>
+    <t>CzSeven</t>
+  </si>
+  <si>
     <t>772 272 784</t>
   </si>
   <si>
@@ -559,10 +606,16 @@
     <t>Test8</t>
   </si>
   <si>
+    <t>10697377</t>
+  </si>
+  <si>
+    <t>CzEight</t>
+  </si>
+  <si>
     <t>773 272 784</t>
   </si>
   <si>
-    <t>Auto 70485837</t>
+    <t>Auto 11621679</t>
   </si>
   <si>
     <t>Store Manager_NEW</t>
@@ -577,6 +630,12 @@
     <t>Test9</t>
   </si>
   <si>
+    <t>10697378</t>
+  </si>
+  <si>
+    <t>CzNine</t>
+  </si>
+  <si>
     <t>774 272 784</t>
   </si>
   <si>
@@ -592,10 +651,16 @@
     <t>Test10</t>
   </si>
   <si>
+    <t>10697379</t>
+  </si>
+  <si>
+    <t>CzTen</t>
+  </si>
+  <si>
     <t>775 272 784</t>
   </si>
   <si>
-    <t>Auto 42819958</t>
+    <t>Auto 47236566</t>
   </si>
   <si>
     <t>Team Manager - Retail_NEW</t>
@@ -610,6 +675,12 @@
     <t>Test11</t>
   </si>
   <si>
+    <t>10697380</t>
+  </si>
+  <si>
+    <t>CzEleven</t>
+  </si>
+  <si>
     <t>776 272 784</t>
   </si>
   <si>
@@ -628,10 +699,16 @@
     <t>Test12</t>
   </si>
   <si>
+    <t>10697381</t>
+  </si>
+  <si>
+    <t>CzTweve</t>
+  </si>
+  <si>
     <t>777 272 784</t>
   </si>
   <si>
-    <t>Auto 67499202</t>
+    <t>Auto 81940803</t>
   </si>
   <si>
     <t>In-Store P&amp;C Manager_NEW</t>
@@ -646,6 +723,12 @@
     <t>Test13</t>
   </si>
   <si>
+    <t>10697382</t>
+  </si>
+  <si>
+    <t>CzThirteen</t>
+  </si>
+  <si>
     <t>778 272 784</t>
   </si>
   <si>
@@ -661,6 +744,12 @@
     <t>Test14</t>
   </si>
   <si>
+    <t>Test failed for 'CzFourteen TwentyFiveMarchThree' Employee: Errors and AlertsAlertNational IDs (Row 2)This national identifier you entered is already in use. Verify that the information is accurate. &amp; find failed Screenshot Path:-&gt;H:\Latest_Workday_Playwright/WorkdayFailedScreenshot/2025-03-02T22-16-16-664Z.png</t>
+  </si>
+  <si>
+    <t>CzFourteen</t>
+  </si>
+  <si>
     <t>779 272 784</t>
   </si>
   <si>
@@ -671,6 +760,12 @@
   </si>
   <si>
     <t>Test15</t>
+  </si>
+  <si>
+    <t>10697384</t>
+  </si>
+  <si>
+    <t>CzFifteen</t>
   </si>
   <si>
     <t>255 Stockroom</t>
@@ -685,54 +780,54 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="12"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="12"/>
       <color theme="1"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
     </font>
     <font>
+      <sz val="14"/>
       <color theme="1"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
-      <sz val="14"/>
-      <name val="Times New Roman"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color theme="1"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
     </font>
     <font>
-      <family val="2"/>
       <sz val="14"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -744,7 +839,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.7999816888943144"/>
+        <fgColor theme="3" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -762,7 +857,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor rgb="FF00FF00"/>
       </patternFill>
     </fill>
     <fill>
@@ -784,16 +879,28 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin"/>
-      <top style="thin"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -1132,10 +1239,10 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:CN17"/>
-  <sheetFormatPr defaultRowHeight="15.6" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15.6" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.21875" style="1" customWidth="1"/>
     <col min="2" max="2" width="12" style="1" customWidth="1"/>
@@ -1216,10 +1323,11 @@
     <col min="77" max="77" width="15" style="1" customWidth="1"/>
     <col min="78" max="78" width="33.6640625" style="1" customWidth="1"/>
     <col min="79" max="79" width="26.88671875" style="1" customWidth="1"/>
-    <col min="80" max="16384" width="8.88671875" style="1" customWidth="1"/>
+    <col min="80" max="80" width="8.88671875" style="1" customWidth="1"/>
+    <col min="81" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" spans="1:92" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:92" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1471,7 +1579,7 @@
       <c r="CM1" s="1"/>
       <c r="CN1" s="1"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:92" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>75</v>
       </c>
@@ -1581,9 +1689,9 @@
       <c r="AJ2" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="AK2" s="12">
+      <c r="AK2" s="12" t="str">
         <f t="shared" ref="AK2:AK16" si="1">AH2</f>
-        <v>NaN</v>
+        <v>N/A</v>
       </c>
       <c r="AL2" s="12">
         <f t="shared" ref="AL2:AL16" si="2">K2</f>
@@ -1715,23 +1823,27 @@
         <v>126</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:92" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
+      <c r="B3" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>77</v>
+      </c>
       <c r="D3" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>79</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H3" s="11" t="s">
         <v>82</v>
@@ -1789,13 +1901,13 @@
         <v>91</v>
       </c>
       <c r="Z3" s="11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AA3" s="8" t="s">
         <v>93</v>
       </c>
       <c r="AB3" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AC3" s="8" t="s">
         <v>95</v>
@@ -1821,9 +1933,9 @@
       <c r="AJ3" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="AK3" s="12">
+      <c r="AK3" s="12" t="str">
         <f t="shared" si="1"/>
-        <v>NaN</v>
+        <v>N/A</v>
       </c>
       <c r="AL3" s="12">
         <f t="shared" si="2"/>
@@ -1834,10 +1946,10 @@
         <v>45597</v>
       </c>
       <c r="AN3" s="11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AO3" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AP3" s="10">
         <v>100</v>
@@ -1937,10 +2049,10 @@
         <v>79</v>
       </c>
       <c r="BV3" s="18" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="BW3" s="18" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="BX3" s="18">
         <v>201</v>
@@ -1955,20 +2067,28 @@
         <v>126</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:92" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
+        <v>138</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>77</v>
+      </c>
       <c r="D4" s="9" t="s">
         <v>78</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="F4" s="8"/>
-      <c r="G4" s="11"/>
+      <c r="F4" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>131</v>
+      </c>
       <c r="H4" s="11" t="s">
         <v>82</v>
       </c>
@@ -2028,13 +2148,13 @@
         <v>92</v>
       </c>
       <c r="AA4" s="8" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AB4" s="8" t="s">
         <v>94</v>
       </c>
       <c r="AC4" s="8" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="AD4" s="10" t="s">
         <v>96</v>
@@ -2043,7 +2163,7 @@
         <v>97</v>
       </c>
       <c r="AF4" s="8" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="AG4" s="15">
         <v>20</v>
@@ -2074,7 +2194,7 @@
         <v>102</v>
       </c>
       <c r="AO4" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="AP4" s="10">
         <v>100</v>
@@ -2144,10 +2264,10 @@
         <v>79</v>
       </c>
       <c r="BL4" s="13" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="BM4" s="13" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="BN4" s="13" t="s">
         <v>118</v>
@@ -2165,7 +2285,7 @@
         <v>1991</v>
       </c>
       <c r="BS4" s="13" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="BT4" s="13" t="s">
         <v>121</v>
@@ -2174,10 +2294,10 @@
         <v>79</v>
       </c>
       <c r="BV4" s="18" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="BW4" s="18" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="BX4" s="18">
         <v>213</v>
@@ -2192,20 +2312,28 @@
         <v>126</v>
       </c>
     </row>
-    <row r="5" ht="15.6" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
+        <v>150</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>77</v>
+      </c>
       <c r="D5" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="F5" s="8"/>
-      <c r="G5" s="11"/>
+      <c r="F5" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>131</v>
+      </c>
       <c r="H5" s="11" t="s">
         <v>82</v>
       </c>
@@ -2262,13 +2390,13 @@
         <v>91</v>
       </c>
       <c r="Z5" s="11" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="AA5" s="8" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AB5" s="8" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="AC5" s="8" t="s">
         <v>95</v>
@@ -2308,10 +2436,10 @@
         <v>45597</v>
       </c>
       <c r="AN5" s="11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AO5" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AP5" s="10">
         <v>100</v>
@@ -2381,10 +2509,10 @@
         <v>79</v>
       </c>
       <c r="BL5" s="13" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="BM5" s="13" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="BN5" s="13" t="s">
         <v>118</v>
@@ -2402,7 +2530,7 @@
         <v>2024</v>
       </c>
       <c r="BS5" s="13" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="BT5" s="13" t="s">
         <v>121</v>
@@ -2411,10 +2539,10 @@
         <v>79</v>
       </c>
       <c r="BV5" s="18" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="BW5" s="18" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="BX5" s="18">
         <v>207</v>
@@ -2429,20 +2557,28 @@
         <v>126</v>
       </c>
     </row>
-    <row r="6" ht="15.6" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
+        <v>160</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>162</v>
+      </c>
       <c r="D6" s="9" t="s">
         <v>78</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="F6" s="8"/>
-      <c r="G6" s="11"/>
+      <c r="F6" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>131</v>
+      </c>
       <c r="H6" s="11" t="s">
         <v>82</v>
       </c>
@@ -2502,22 +2638,22 @@
         <v>92</v>
       </c>
       <c r="AA6" s="8" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="AB6" s="8" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="AC6" s="8" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="AD6" s="10" t="s">
         <v>96</v>
       </c>
       <c r="AE6" s="10" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="AF6" s="8" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="AG6" s="15">
         <v>16</v>
@@ -2527,7 +2663,7 @@
         <v>45962</v>
       </c>
       <c r="AI6" s="11" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="AJ6" s="11" t="s">
         <v>101</v>
@@ -2548,7 +2684,7 @@
         <v>102</v>
       </c>
       <c r="AO6" s="8" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="AP6" s="10">
         <v>100</v>
@@ -2648,10 +2784,10 @@
         <v>79</v>
       </c>
       <c r="BV6" s="18" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="BW6" s="18" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="BX6" s="18">
         <v>211</v>
@@ -2666,22 +2802,30 @@
         <v>126</v>
       </c>
     </row>
-    <row r="7" ht="15.6" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
+        <v>172</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>77</v>
+      </c>
       <c r="D7" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="F7" s="8"/>
-      <c r="G7" s="11"/>
+      <c r="F7" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>131</v>
+      </c>
       <c r="H7" s="11" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="I7" s="11" t="s">
         <v>83</v>
@@ -2736,16 +2880,16 @@
         <v>91</v>
       </c>
       <c r="Z7" s="11" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="AA7" s="8" t="s">
         <v>93</v>
       </c>
       <c r="AB7" s="8" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="AC7" s="8" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="AD7" s="10" t="s">
         <v>96</v>
@@ -2768,9 +2912,9 @@
       <c r="AJ7" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="AK7" s="12">
+      <c r="AK7" s="12" t="str">
         <f t="shared" si="1"/>
-        <v>NaN</v>
+        <v>N/A</v>
       </c>
       <c r="AL7" s="12">
         <f t="shared" si="2"/>
@@ -2781,10 +2925,10 @@
         <v>45597</v>
       </c>
       <c r="AN7" s="11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AO7" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AP7" s="10">
         <v>100</v>
@@ -2854,10 +2998,10 @@
         <v>79</v>
       </c>
       <c r="BL7" s="13" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="BM7" s="13" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="BN7" s="13" t="s">
         <v>118</v>
@@ -2875,7 +3019,7 @@
         <v>2000</v>
       </c>
       <c r="BS7" s="13" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="BT7" s="13" t="s">
         <v>121</v>
@@ -2884,10 +3028,10 @@
         <v>79</v>
       </c>
       <c r="BV7" s="18" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="BW7" s="18" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="BX7" s="18">
         <v>211</v>
@@ -2902,22 +3046,30 @@
         <v>126</v>
       </c>
     </row>
-    <row r="8" ht="15.6" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
+        <v>183</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>77</v>
+      </c>
       <c r="D8" s="9" t="s">
         <v>78</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="F8" s="8"/>
-      <c r="G8" s="11"/>
+      <c r="F8" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>131</v>
+      </c>
       <c r="H8" s="11" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="I8" s="11" t="s">
         <v>83</v>
@@ -2975,13 +3127,13 @@
         <v>92</v>
       </c>
       <c r="AA8" s="8" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AB8" s="8" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="AC8" s="8" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="AD8" s="10" t="s">
         <v>96</v>
@@ -3021,7 +3173,7 @@
         <v>102</v>
       </c>
       <c r="AO8" s="8" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="AP8" s="10">
         <v>100</v>
@@ -3121,10 +3273,10 @@
         <v>79</v>
       </c>
       <c r="BV8" s="18" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="BW8" s="18" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="BX8" s="18">
         <v>213</v>
@@ -3139,22 +3291,30 @@
         <v>126</v>
       </c>
     </row>
-    <row r="9" ht="15.6" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
+        <v>191</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>77</v>
+      </c>
       <c r="D9" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="F9" s="8"/>
-      <c r="G9" s="11"/>
+      <c r="F9" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>131</v>
+      </c>
       <c r="H9" s="11" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="I9" s="11" t="s">
         <v>83</v>
@@ -3209,13 +3369,13 @@
         <v>91</v>
       </c>
       <c r="Z9" s="11" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="AA9" s="8" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AB9" s="8" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="AC9" s="8" t="s">
         <v>95</v>
@@ -3255,10 +3415,10 @@
         <v>45597</v>
       </c>
       <c r="AN9" s="11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AO9" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AP9" s="10">
         <v>100</v>
@@ -3328,10 +3488,10 @@
         <v>79</v>
       </c>
       <c r="BL9" s="13" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="BM9" s="13" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="BN9" s="13" t="s">
         <v>118</v>
@@ -3349,7 +3509,7 @@
         <v>1991</v>
       </c>
       <c r="BS9" s="13" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="BT9" s="13" t="s">
         <v>121</v>
@@ -3358,10 +3518,10 @@
         <v>79</v>
       </c>
       <c r="BV9" s="18" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="BW9" s="18" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="BX9" s="18">
         <v>211</v>
@@ -3376,22 +3536,30 @@
         <v>126</v>
       </c>
     </row>
-    <row r="10" ht="15.6" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
+        <v>199</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>77</v>
+      </c>
       <c r="D10" s="9" t="s">
         <v>78</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="F10" s="8"/>
-      <c r="G10" s="11"/>
+      <c r="F10" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>131</v>
+      </c>
       <c r="H10" s="11" t="s">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="I10" s="11" t="s">
         <v>83</v>
@@ -3452,10 +3620,10 @@
         <v>93</v>
       </c>
       <c r="AB10" s="8" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="AC10" s="8" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="AD10" s="10" t="s">
         <v>96</v>
@@ -3464,7 +3632,7 @@
         <v>97</v>
       </c>
       <c r="AF10" s="8" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="AG10" s="15">
         <v>20</v>
@@ -3478,9 +3646,9 @@
       <c r="AJ10" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="AK10" s="12">
+      <c r="AK10" s="12" t="str">
         <f t="shared" si="1"/>
-        <v>NaN</v>
+        <v>N/A</v>
       </c>
       <c r="AL10" s="12">
         <f t="shared" si="2"/>
@@ -3494,7 +3662,7 @@
         <v>102</v>
       </c>
       <c r="AO10" s="8" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="AP10" s="10">
         <v>100</v>
@@ -3564,10 +3732,10 @@
         <v>79</v>
       </c>
       <c r="BL10" s="13" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="BM10" s="13" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="BN10" s="13" t="s">
         <v>118</v>
@@ -3585,7 +3753,7 @@
         <v>2024</v>
       </c>
       <c r="BS10" s="13" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="BT10" s="13" t="s">
         <v>121</v>
@@ -3594,10 +3762,10 @@
         <v>79</v>
       </c>
       <c r="BV10" s="18" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="BW10" s="18" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="BX10" s="18">
         <v>213</v>
@@ -3612,22 +3780,30 @@
         <v>126</v>
       </c>
     </row>
-    <row r="11" ht="15.6" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
+        <v>206</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>77</v>
+      </c>
       <c r="D11" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="F11" s="8"/>
-      <c r="G11" s="11"/>
+      <c r="F11" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>131</v>
+      </c>
       <c r="H11" s="11" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="I11" s="11" t="s">
         <v>83</v>
@@ -3682,13 +3858,13 @@
         <v>91</v>
       </c>
       <c r="Z11" s="11" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="AA11" s="8" t="s">
         <v>93</v>
       </c>
       <c r="AB11" s="8" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="AC11" s="8" t="s">
         <v>95</v>
@@ -3714,9 +3890,9 @@
       <c r="AJ11" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="AK11" s="12">
+      <c r="AK11" s="12" t="str">
         <f t="shared" si="1"/>
-        <v>NaN</v>
+        <v>N/A</v>
       </c>
       <c r="AL11" s="12">
         <f t="shared" si="2"/>
@@ -3727,10 +3903,10 @@
         <v>45597</v>
       </c>
       <c r="AN11" s="11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AO11" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AP11" s="10">
         <v>100</v>
@@ -3830,10 +4006,10 @@
         <v>79</v>
       </c>
       <c r="BV11" s="18" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="BW11" s="18" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="BX11" s="18">
         <v>201</v>
@@ -3848,22 +4024,30 @@
         <v>126</v>
       </c>
     </row>
-    <row r="12" ht="15.6" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
+        <v>214</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>77</v>
+      </c>
       <c r="D12" s="9" t="s">
         <v>78</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="F12" s="8"/>
-      <c r="G12" s="11"/>
+      <c r="F12" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>131</v>
+      </c>
       <c r="H12" s="11" t="s">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="I12" s="11" t="s">
         <v>83</v>
@@ -3921,13 +4105,13 @@
         <v>92</v>
       </c>
       <c r="AA12" s="8" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AB12" s="8" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="AC12" s="8" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="AD12" s="10" t="s">
         <v>96</v>
@@ -3967,7 +4151,7 @@
         <v>102</v>
       </c>
       <c r="AO12" s="8" t="s">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="AP12" s="10">
         <v>100</v>
@@ -4037,10 +4221,10 @@
         <v>79</v>
       </c>
       <c r="BL12" s="13" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="BM12" s="13" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="BN12" s="13" t="s">
         <v>118</v>
@@ -4058,7 +4242,7 @@
         <v>2000</v>
       </c>
       <c r="BS12" s="13" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="BT12" s="13" t="s">
         <v>121</v>
@@ -4067,10 +4251,10 @@
         <v>79</v>
       </c>
       <c r="BV12" s="18" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="BW12" s="18" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
       <c r="BX12" s="18">
         <v>213</v>
@@ -4085,22 +4269,30 @@
         <v>126</v>
       </c>
     </row>
-    <row r="13" ht="15.6" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
+        <v>222</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>77</v>
+      </c>
       <c r="D13" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="F13" s="8"/>
-      <c r="G13" s="11"/>
+      <c r="F13" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>131</v>
+      </c>
       <c r="H13" s="11" t="s">
-        <v>203</v>
+        <v>225</v>
       </c>
       <c r="I13" s="11" t="s">
         <v>83</v>
@@ -4155,13 +4347,13 @@
         <v>91</v>
       </c>
       <c r="Z13" s="11" t="s">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="AA13" s="8" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AB13" s="8" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="AC13" s="8" t="s">
         <v>95</v>
@@ -4201,10 +4393,10 @@
         <v>45597</v>
       </c>
       <c r="AN13" s="11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AO13" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AP13" s="10">
         <v>100</v>
@@ -4304,10 +4496,10 @@
         <v>79</v>
       </c>
       <c r="BV13" s="18" t="s">
-        <v>206</v>
+        <v>228</v>
       </c>
       <c r="BW13" s="18" t="s">
-        <v>207</v>
+        <v>229</v>
       </c>
       <c r="BX13" s="18">
         <v>209</v>
@@ -4322,22 +4514,30 @@
         <v>126</v>
       </c>
     </row>
-    <row r="14" ht="15.6" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
+        <v>230</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>77</v>
+      </c>
       <c r="D14" s="9" t="s">
         <v>78</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="F14" s="8"/>
-      <c r="G14" s="11"/>
+      <c r="F14" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>131</v>
+      </c>
       <c r="H14" s="11" t="s">
-        <v>209</v>
+        <v>233</v>
       </c>
       <c r="I14" s="11" t="s">
         <v>83</v>
@@ -4398,10 +4598,10 @@
         <v>93</v>
       </c>
       <c r="AB14" s="8" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="AC14" s="8" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="AD14" s="10" t="s">
         <v>96</v>
@@ -4410,7 +4610,7 @@
         <v>97</v>
       </c>
       <c r="AF14" s="8" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="AG14" s="15">
         <v>24</v>
@@ -4424,9 +4624,9 @@
       <c r="AJ14" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="AK14" s="12">
+      <c r="AK14" s="12" t="str">
         <f t="shared" si="1"/>
-        <v>NaN</v>
+        <v>N/A</v>
       </c>
       <c r="AL14" s="12">
         <f t="shared" si="2"/>
@@ -4440,7 +4640,7 @@
         <v>102</v>
       </c>
       <c r="AO14" s="8" t="s">
-        <v>210</v>
+        <v>234</v>
       </c>
       <c r="AP14" s="10">
         <v>100</v>
@@ -4510,10 +4710,10 @@
         <v>79</v>
       </c>
       <c r="BL14" s="13" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="BM14" s="13" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="BN14" s="13" t="s">
         <v>118</v>
@@ -4531,7 +4731,7 @@
         <v>1991</v>
       </c>
       <c r="BS14" s="13" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="BT14" s="13" t="s">
         <v>121</v>
@@ -4540,10 +4740,10 @@
         <v>79</v>
       </c>
       <c r="BV14" s="18" t="s">
-        <v>211</v>
+        <v>235</v>
       </c>
       <c r="BW14" s="18" t="s">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="BX14" s="18">
         <v>211</v>
@@ -4558,22 +4758,30 @@
         <v>126</v>
       </c>
     </row>
-    <row r="15" ht="15.6" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
+        <v>237</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>162</v>
+      </c>
       <c r="D15" s="9" t="s">
         <v>78</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="F15" s="8"/>
-      <c r="G15" s="11"/>
+      <c r="F15" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>131</v>
+      </c>
       <c r="H15" s="11" t="s">
-        <v>214</v>
+        <v>240</v>
       </c>
       <c r="I15" s="11" t="s">
         <v>83</v>
@@ -4631,10 +4839,10 @@
         <v>92</v>
       </c>
       <c r="AA15" s="8" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AB15" s="8" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="AC15" s="8" t="s">
         <v>95</v>
@@ -4677,7 +4885,7 @@
         <v>102</v>
       </c>
       <c r="AO15" s="8" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="AP15" s="10">
         <v>100</v>
@@ -4747,10 +4955,10 @@
         <v>79</v>
       </c>
       <c r="BL15" s="13" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="BM15" s="13" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="BN15" s="13" t="s">
         <v>118</v>
@@ -4768,7 +4976,7 @@
         <v>2024</v>
       </c>
       <c r="BS15" s="13" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="BT15" s="13" t="s">
         <v>121</v>
@@ -4777,10 +4985,10 @@
         <v>79</v>
       </c>
       <c r="BV15" s="18" t="s">
-        <v>215</v>
+        <v>241</v>
       </c>
       <c r="BW15" s="18" t="s">
-        <v>216</v>
+        <v>242</v>
       </c>
       <c r="BX15" s="18">
         <v>213</v>
@@ -4795,22 +5003,30 @@
         <v>126</v>
       </c>
     </row>
-    <row r="16" ht="15.6" customHeight="1" spans="1:79" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:92" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
+        <v>243</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>77</v>
+      </c>
       <c r="D16" s="9" t="s">
         <v>78</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="F16" s="8"/>
-      <c r="G16" s="11"/>
+      <c r="F16" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>131</v>
+      </c>
       <c r="H16" s="11" t="s">
-        <v>214</v>
+        <v>240</v>
       </c>
       <c r="I16" s="11" t="s">
         <v>83</v>
@@ -4874,7 +5090,7 @@
         <v>94</v>
       </c>
       <c r="AC16" s="8" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="AD16" s="10" t="s">
         <v>96</v>
@@ -4897,9 +5113,9 @@
       <c r="AJ16" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="AK16" s="12">
+      <c r="AK16" s="12" t="str">
         <f t="shared" si="1"/>
-        <v>NaN</v>
+        <v>N/A</v>
       </c>
       <c r="AL16" s="12">
         <f t="shared" si="2"/>
@@ -4913,7 +5129,7 @@
         <v>102</v>
       </c>
       <c r="AO16" s="8" t="s">
-        <v>218</v>
+        <v>246</v>
       </c>
       <c r="AP16" s="10">
         <v>100</v>
@@ -4983,10 +5199,10 @@
         <v>79</v>
       </c>
       <c r="BL16" s="13" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="BM16" s="13" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="BN16" s="13" t="s">
         <v>118</v>
@@ -5004,7 +5220,7 @@
         <v>2024</v>
       </c>
       <c r="BS16" s="13" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="BT16" s="13" t="s">
         <v>121</v>
@@ -5013,10 +5229,10 @@
         <v>79</v>
       </c>
       <c r="BV16" s="18" t="s">
-        <v>219</v>
+        <v>247</v>
       </c>
       <c r="BW16" s="18" t="s">
-        <v>220</v>
+        <v>248</v>
       </c>
       <c r="BX16" s="18">
         <v>211</v>
@@ -5031,54 +5247,30 @@
         <v>126</v>
       </c>
     </row>
-    <row r="17" ht="15.6" customHeight="1" spans="46:51" x14ac:dyDescent="0.25">
+    <row r="17" spans="46:51" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="AT17" s="19"/>
       <c r="AY17" s="19"/>
     </row>
   </sheetData>
-  <dataValidations count="12">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ10:AJ16">
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ10:AJ16 Y10:Y16 W10:W16 T10:T16" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>INDIRECT($D1)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ2:AJ16">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ2:AJ16 Y2:Y16 W2:W16 T2:T16" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>INDIRECT($D1)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH10:BH16">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH10:BH16 J10:J16" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>INDIRECT($D2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH2:BH16">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH2:BH16 J2:J16" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>INDIRECT($D2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J10:J16">
-      <formula1>INDIRECT($D2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J16">
-      <formula1>INDIRECT($D2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T10:T16">
-      <formula1>INDIRECT($D1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T16">
-      <formula1>INDIRECT($D1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W10:W16">
-      <formula1>INDIRECT($D1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W16">
-      <formula1>INDIRECT($D1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y10:Y16">
-      <formula1>INDIRECT($D1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Y16">
-      <formula1>INDIRECT($D1)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="V2" r:id="rId1"/>
-    <hyperlink ref="V3" r:id="rId2"/>
+    <hyperlink ref="V2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="V3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="0" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="0" r:id="rId3"/>
 </worksheet>
 </file>